--- a/data/trans_orig/SE_ADU-Clase-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2007</t>
+          <t>Sexo adulto elegido en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,47 +768,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>304711</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>306680</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>306680</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>279649</t>
+          <t>279449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>333818</t>
+          <t>332842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471781</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446639</t>
+          <t>447615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>500808</t>
+          <t>501008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>369904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>371865</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>371865</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>343563</t>
+          <t>343025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>398933</t>
+          <t>399276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -1189,82 +1189,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364927</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>366934</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>366934</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339866</t>
+          <t>339523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395236</t>
+          <t>395774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>167782</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145982</t>
+          <t>145050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>190858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1532,82 +1532,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>542389</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>542389</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518448</t>
+          <t>519313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564189</t>
+          <t>565121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,47 +1797,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>712312</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>714285</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>714285</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>666498</t>
+          <t>669052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>755222</t>
+          <t>757143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1236393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1238334</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1197398</t>
+          <t>1195477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286122</t>
+          <t>1283568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,47 +2140,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>566730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>568752</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>568752</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>535969</t>
+          <t>539352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>599128</t>
+          <t>599584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -2218,82 +2218,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>350555</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>350555</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320179</t>
+          <t>319723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383338</t>
+          <t>379955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,47 +2483,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1246824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>1248760</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1248760</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1218806</t>
+          <t>1218122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1278066</t>
+          <t>1278942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268894</t>
+          <t>268018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>328154</t>
+          <t>328838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,47 +2826,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3376156</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>3378124</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3296</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3378124</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3299949</t>
+          <t>3294939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3462303</t>
+          <t>3466995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -2904,82 +2904,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3268232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>3270190</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3207</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3270190</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3186011</t>
+          <t>3181319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3348365</t>
+          <t>3353375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2012</t>
+          <t>Sexo adulto elegido en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,47 +3403,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>312329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>314454</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>288492</t>
+          <t>286455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>341609</t>
+          <t>343403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -3481,82 +3481,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>437211</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2125</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>437211</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410056</t>
+          <t>408262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>463173</t>
+          <t>465210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,47 +3746,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>338011</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>338011</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308613</t>
+          <t>307681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>366972</t>
+          <t>367861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -3824,82 +3824,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>418797</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>418797</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389836</t>
+          <t>388947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448195</t>
+          <t>449127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,47 +4089,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>260129</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>260129</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231223</t>
+          <t>231586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286750</t>
+          <t>289099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -4167,82 +4167,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>629415</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>629415</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602794</t>
+          <t>600445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658321</t>
+          <t>657958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>764589</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>766657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>721007</t>
+          <t>720135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>811458</t>
+          <t>810999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -4510,82 +4510,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1156956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>1159009</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1159009</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1114209</t>
+          <t>1114668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1204660</t>
+          <t>1205532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,47 +4775,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>759445</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>761522</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>761522</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>722028</t>
+          <t>727043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>793973</t>
+          <t>800019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -4853,82 +4853,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>508587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>510596</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2077</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>510596</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>478145</t>
+          <t>472099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>550090</t>
+          <t>545075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,47 +5118,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1107312</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>1109351</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1109351</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1078215</t>
+          <t>1077955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1137326</t>
+          <t>1136841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -5196,82 +5196,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>266882</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>266882</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238907</t>
+          <t>239392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298018</t>
+          <t>298278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,47 +5461,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3548053</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>3550125</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3290</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3550125</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3469220</t>
+          <t>3455476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3634790</t>
+          <t>3637389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -5539,82 +5539,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3419860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>3421910</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3421910</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3337245</t>
+          <t>3334646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3502815</t>
+          <t>3516559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2016</t>
+          <t>Sexo adulto elegido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,47 +6038,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>345054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>347055</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>347055</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319326</t>
+          <t>320253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>378984</t>
+          <t>376228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -6116,82 +6116,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>429092</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>429092</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>397163</t>
+          <t>399919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>456821</t>
+          <t>455894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,47 +6381,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>372273</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>372273</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>344987</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401530</t>
+          <t>402568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -6459,82 +6459,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>377227</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>377227</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347970</t>
+          <t>346932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404513</t>
+          <t>404923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,47 +6724,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>166123</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145022</t>
+          <t>144414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191708</t>
+          <t>191815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519922</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496328</t>
+          <t>496221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543014</t>
+          <t>543622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,47 +7067,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>823891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>825876</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>825876</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>781646</t>
+          <t>784905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>871623</t>
+          <t>873500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -7145,82 +7145,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1147638</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>1149638</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1149638</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1103891</t>
+          <t>1102014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1193868</t>
+          <t>1190609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,27%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,47 +7410,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>736219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>738244</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>738244</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>698539</t>
+          <t>697924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>773514</t>
+          <t>773818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -7488,82 +7488,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>618713</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>620706</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>620706</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>585436</t>
+          <t>585132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>660411</t>
+          <t>661026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,47 +7753,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1079933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>1082025</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1082025</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1046648</t>
+          <t>1051546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1109141</t>
+          <t>1112407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -7831,82 +7831,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>287145</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>287145</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>260029</t>
+          <t>256763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322522</t>
+          <t>317624</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,47 +8096,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3529557</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>3531596</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3531596</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3447097</t>
+          <t>3453510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3614058</t>
+          <t>3623934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -8174,82 +8174,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3383706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>3385722</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3385722</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3303260</t>
+          <t>3293384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3470221</t>
+          <t>3463808</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2023</t>
+          <t>Sexo adulto elegido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,47 +8673,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>446216</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>447467</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>447467</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416439</t>
+          <t>417700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474272</t>
+          <t>474094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -8751,82 +8751,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>505212</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>505212</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478407</t>
+          <t>478585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536240</t>
+          <t>534979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,47 +9016,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>381337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>382580</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>382580</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356843</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>412991</t>
+          <t>408902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -9094,82 +9094,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>452213</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>452213</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421802</t>
+          <t>425891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477950</t>
+          <t>479612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,47 +9359,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165806</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>166911</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>74401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243601</t>
+          <t>243146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -9437,82 +9437,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665640</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>668264</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>668264</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>591574</t>
+          <t>592029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>766433</t>
+          <t>760774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>976568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>844125</t>
+          <t>845701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1256001</t>
+          <t>1323097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -9780,82 +9780,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1033043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>1034819</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1034819</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>756911</t>
+          <t>689815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168787</t>
+          <t>1167211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,47 +10045,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>840083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>841335</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>841335</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>794697</t>
+          <t>790658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>925506</t>
+          <t>932912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -10123,82 +10123,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>473382</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>475046</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>475046</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390875</t>
+          <t>383469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>521684</t>
+          <t>525723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,47 +10388,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>760111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>761371</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>761371</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>717144</t>
+          <t>716908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>800586</t>
+          <t>800829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -10466,82 +10466,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>240507</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>240507</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201292</t>
+          <t>201049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284734</t>
+          <t>284970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,47 +10731,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3576448</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>3577758</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3577758</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3173956</t>
+          <t>3172597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3881671</t>
+          <t>3839789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -10809,82 +10809,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3374096</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>3376060</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3376060</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3072147</t>
+          <t>3114029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3779862</t>
+          <t>3781221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/SE_ADU-Clase-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Clase-trans_orig.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>279449</t>
+          <t>279921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332842</t>
+          <t>335021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>447615</t>
+          <t>445436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>501008</t>
+          <t>500536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>343025</t>
+          <t>344496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399276</t>
+          <t>397848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339523</t>
+          <t>340951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395774</t>
+          <t>394303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>145350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190858</t>
+          <t>189720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519313</t>
+          <t>520451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565121</t>
+          <t>564821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>669052</t>
+          <t>670525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>757143</t>
+          <t>758062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195477</t>
+          <t>1194558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1283568</t>
+          <t>1282095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539352</t>
+          <t>539618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>599584</t>
+          <t>598692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319723</t>
+          <t>320615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379955</t>
+          <t>379689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1218122</t>
+          <t>1214651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1278942</t>
+          <t>1276403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268018</t>
+          <t>270557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>328838</t>
+          <t>332309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3294939</t>
+          <t>3293826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3466995</t>
+          <t>3461927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3181319</t>
+          <t>3186387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3353375</t>
+          <t>3354488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>286455</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343403</t>
+          <t>342487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>408262</t>
+          <t>409178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>465210</t>
+          <t>465408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307681</t>
+          <t>307741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>367861</t>
+          <t>366301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388947</t>
+          <t>390507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449127</t>
+          <t>449067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>229342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289099</t>
+          <t>287231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600445</t>
+          <t>602313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657958</t>
+          <t>660202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>720135</t>
+          <t>722378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>810999</t>
+          <t>805622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1114668</t>
+          <t>1120045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1205532</t>
+          <t>1203289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>727043</t>
+          <t>725773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>800019</t>
+          <t>795978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>472099</t>
+          <t>476140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>545075</t>
+          <t>546345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1077955</t>
+          <t>1080300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1136841</t>
+          <t>1136545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239392</t>
+          <t>239688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298278</t>
+          <t>295933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3455476</t>
+          <t>3465633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3637389</t>
+          <t>3636283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3334646</t>
+          <t>3335752</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3516559</t>
+          <t>3506402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>320253</t>
+          <t>315537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376228</t>
+          <t>374065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399919</t>
+          <t>402082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>455894</t>
+          <t>460610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>343410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402568</t>
+          <t>400249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346932</t>
+          <t>349251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404923</t>
+          <t>406090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144414</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191815</t>
+          <t>191744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496221</t>
+          <t>496292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543622</t>
+          <t>544032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>784905</t>
+          <t>779516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>873500</t>
+          <t>867256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1102014</t>
+          <t>1108258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1190609</t>
+          <t>1195998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>697924</t>
+          <t>700829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>773818</t>
+          <t>771925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>585132</t>
+          <t>587025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>661026</t>
+          <t>658121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1051546</t>
+          <t>1052354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1112407</t>
+          <t>1116160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>256763</t>
+          <t>253010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317624</t>
+          <t>316816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3453510</t>
+          <t>3445700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3623934</t>
+          <t>3610789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3293384</t>
+          <t>3306529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3463808</t>
+          <t>3471618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417700</t>
+          <t>459864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474094</t>
+          <t>520102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478585</t>
+          <t>518927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>534979</t>
+          <t>579165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>394685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408902</t>
+          <t>448081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425891</t>
+          <t>458274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479612</t>
+          <t>511670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74401</t>
+          <t>168498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243146</t>
+          <t>210232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592029</t>
+          <t>448877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>760774</t>
+          <t>490611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>978093</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>845701</t>
+          <t>819577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1323097</t>
+          <t>905942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689815</t>
+          <t>1087112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1167211</t>
+          <t>1173477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>790658</t>
+          <t>793417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>932912</t>
+          <t>868852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383469</t>
+          <t>529962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>525723</t>
+          <t>605397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>716908</t>
+          <t>804516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>800829</t>
+          <t>881712</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201049</t>
+          <t>199797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284970</t>
+          <t>276993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3172597</t>
+          <t>3560883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3839789</t>
+          <t>3720726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3114029</t>
+          <t>3357143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3781221</t>
+          <t>3516986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
